--- a/output_diffuser/diffuser_100_products.xlsx
+++ b/output_diffuser/diffuser_100_products.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -545,13 +545,13 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>spring</t>
+          <t>etc</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
-          <t>spring</t>
+          <t>etc</t>
         </is>
       </c>
       <c r="M2" t="n">
@@ -560,15 +560,9 @@
       <c r="N2" t="n">
         <v>900</v>
       </c>
-      <c r="O2" t="b">
-        <v>0</v>
-      </c>
-      <c r="P2" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q2" t="b">
-        <v>0</v>
-      </c>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -627,15 +621,9 @@
       <c r="N3" t="n">
         <v>1350</v>
       </c>
-      <c r="O3" t="b">
-        <v>0</v>
-      </c>
-      <c r="P3" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q3" t="b">
-        <v>0</v>
-      </c>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -679,13 +667,13 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>spring</t>
+          <t>autumn</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
-          <t>spring</t>
+          <t>autumn</t>
         </is>
       </c>
       <c r="M4" t="n">
@@ -694,15 +682,9 @@
       <c r="N4" t="n">
         <v>1350</v>
       </c>
-      <c r="O4" t="b">
-        <v>0</v>
-      </c>
-      <c r="P4" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q4" t="b">
-        <v>0</v>
-      </c>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -741,7 +723,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>오렌지</t>
+          <t>핑크</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -761,15 +743,9 @@
       <c r="N5" t="n">
         <v>1350</v>
       </c>
-      <c r="O5" t="b">
-        <v>0</v>
-      </c>
-      <c r="P5" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="b">
-        <v>0</v>
-      </c>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -808,7 +784,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>옐로</t>
+          <t>핑크</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -828,15 +804,9 @@
       <c r="N6" t="n">
         <v>1350</v>
       </c>
-      <c r="O6" t="b">
-        <v>0</v>
-      </c>
-      <c r="P6" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="b">
-        <v>0</v>
-      </c>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -895,15 +865,9 @@
       <c r="N7" t="n">
         <v>900</v>
       </c>
-      <c r="O7" t="b">
-        <v>0</v>
-      </c>
-      <c r="P7" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="b">
-        <v>0</v>
-      </c>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -942,18 +906,18 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>페일베이지</t>
+          <t>베이지</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>spring</t>
+          <t>autumn</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
-          <t>spring</t>
+          <t>autumn</t>
         </is>
       </c>
       <c r="M8" t="n">
@@ -962,15 +926,9 @@
       <c r="N8" t="n">
         <v>4410</v>
       </c>
-      <c r="O8" t="b">
-        <v>0</v>
-      </c>
-      <c r="P8" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="b">
-        <v>0</v>
-      </c>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1029,15 +987,9 @@
       <c r="N9" t="n">
         <v>3510</v>
       </c>
-      <c r="O9" t="b">
-        <v>0</v>
-      </c>
-      <c r="P9" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="b">
-        <v>0</v>
-      </c>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1096,15 +1048,9 @@
       <c r="N10" t="n">
         <v>2610</v>
       </c>
-      <c r="O10" t="b">
-        <v>0</v>
-      </c>
-      <c r="P10" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="b">
-        <v>0</v>
-      </c>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1143,7 +1089,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>라이트그린</t>
+          <t>그린</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1163,15 +1109,9 @@
       <c r="N11" t="n">
         <v>900</v>
       </c>
-      <c r="O11" t="b">
-        <v>0</v>
-      </c>
-      <c r="P11" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="b">
-        <v>0</v>
-      </c>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1210,18 +1150,18 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>레드오렌지 옐로브라운</t>
+          <t>우드</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>spring</t>
+          <t>autumn</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr">
         <is>
-          <t>spring</t>
+          <t>autumn</t>
         </is>
       </c>
       <c r="M12" t="n">
@@ -1230,15 +1170,9 @@
       <c r="N12" t="n">
         <v>17910</v>
       </c>
-      <c r="O12" t="b">
-        <v>0</v>
-      </c>
-      <c r="P12" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="b">
-        <v>0</v>
-      </c>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1277,18 +1211,18 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>블루 라이트옐로</t>
+          <t>블루</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>spring</t>
+          <t>summer</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr">
         <is>
-          <t>spring</t>
+          <t>summer</t>
         </is>
       </c>
       <c r="M13" t="n">
@@ -1297,15 +1231,9 @@
       <c r="N13" t="n">
         <v>17910</v>
       </c>
-      <c r="O13" t="b">
-        <v>0</v>
-      </c>
-      <c r="P13" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="b">
-        <v>0</v>
-      </c>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1344,18 +1272,18 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>페일베이지</t>
+          <t>베이지</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>spring</t>
+          <t>autumn</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr">
         <is>
-          <t>spring</t>
+          <t>autumn</t>
         </is>
       </c>
       <c r="M14" t="n">
@@ -1364,15 +1292,9 @@
       <c r="N14" t="n">
         <v>900</v>
       </c>
-      <c r="O14" t="b">
-        <v>0</v>
-      </c>
-      <c r="P14" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="b">
-        <v>0</v>
-      </c>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1411,18 +1333,18 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>라이트베이지</t>
+          <t>베이지</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>spring</t>
+          <t>autumn</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr">
         <is>
-          <t>spring</t>
+          <t>autumn</t>
         </is>
       </c>
       <c r="M15" t="n">
@@ -1431,15 +1353,9 @@
       <c r="N15" t="n">
         <v>900</v>
       </c>
-      <c r="O15" t="b">
-        <v>0</v>
-      </c>
-      <c r="P15" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="b">
-        <v>0</v>
-      </c>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1478,18 +1394,18 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>도트 브라운</t>
+          <t>우드</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>spring</t>
+          <t>autumn</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr">
         <is>
-          <t>spring</t>
+          <t>autumn</t>
         </is>
       </c>
       <c r="M16" t="n">
@@ -1498,15 +1414,9 @@
       <c r="N16" t="n">
         <v>17910</v>
       </c>
-      <c r="O16" t="b">
-        <v>0</v>
-      </c>
-      <c r="P16" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="b">
-        <v>0</v>
-      </c>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1545,18 +1455,18 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>라이트오렌지</t>
+          <t>화이트</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>spring</t>
+          <t>etc</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr">
         <is>
-          <t>spring</t>
+          <t>etc</t>
         </is>
       </c>
       <c r="M17" t="n">
@@ -1565,15 +1475,9 @@
       <c r="N17" t="n">
         <v>3510</v>
       </c>
-      <c r="O17" t="b">
-        <v>0</v>
-      </c>
-      <c r="P17" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="b">
-        <v>0</v>
-      </c>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1612,18 +1516,18 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>프레쉬리넨 화이트</t>
+          <t>화이트</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>spring</t>
+          <t>etc</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr">
         <is>
-          <t>spring</t>
+          <t>etc</t>
         </is>
       </c>
       <c r="M18" t="n">
@@ -1632,15 +1536,9 @@
       <c r="N18" t="n">
         <v>3510</v>
       </c>
-      <c r="O18" t="b">
-        <v>0</v>
-      </c>
-      <c r="P18" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q18" t="b">
-        <v>0</v>
-      </c>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1679,7 +1577,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>레드베리 라이트핑크</t>
+          <t>핑크</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1699,15 +1597,9 @@
       <c r="N19" t="n">
         <v>4410</v>
       </c>
-      <c r="O19" t="b">
-        <v>0</v>
-      </c>
-      <c r="P19" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="b">
-        <v>0</v>
-      </c>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1766,15 +1658,9 @@
       <c r="N20" t="n">
         <v>4410</v>
       </c>
-      <c r="O20" t="b">
-        <v>0</v>
-      </c>
-      <c r="P20" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q20" t="b">
-        <v>0</v>
-      </c>
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" t="inlineStr"/>
+      <c r="Q20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1813,18 +1699,18 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>샌달우드 파촐리 브라운</t>
+          <t>우드</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>spring</t>
+          <t>autumn</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr">
         <is>
-          <t>spring</t>
+          <t>autumn</t>
         </is>
       </c>
       <c r="M21" t="n">
@@ -1833,15 +1719,9 @@
       <c r="N21" t="n">
         <v>3510</v>
       </c>
-      <c r="O21" t="b">
-        <v>0</v>
-      </c>
-      <c r="P21" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q21" t="b">
-        <v>0</v>
-      </c>
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" t="inlineStr"/>
+      <c r="Q21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1880,7 +1760,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>라이트그린</t>
+          <t>그린</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1900,15 +1780,9 @@
       <c r="N22" t="n">
         <v>2250</v>
       </c>
-      <c r="O22" t="b">
-        <v>0</v>
-      </c>
-      <c r="P22" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q22" t="b">
-        <v>0</v>
-      </c>
+      <c r="O22" t="inlineStr"/>
+      <c r="P22" t="inlineStr"/>
+      <c r="Q22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1947,7 +1821,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>라이트그린</t>
+          <t>그린</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -1967,15 +1841,9 @@
       <c r="N23" t="n">
         <v>900</v>
       </c>
-      <c r="O23" t="b">
-        <v>0</v>
-      </c>
-      <c r="P23" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q23" t="b">
-        <v>0</v>
-      </c>
+      <c r="O23" t="inlineStr"/>
+      <c r="P23" t="inlineStr"/>
+      <c r="Q23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2014,18 +1882,18 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>브라이트옐로우그린</t>
+          <t>옐로우</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>spring</t>
+          <t>summer</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr">
         <is>
-          <t>spring</t>
+          <t>summer</t>
         </is>
       </c>
       <c r="M24" t="n">
@@ -2034,15 +1902,9 @@
       <c r="N24" t="n">
         <v>8010</v>
       </c>
-      <c r="O24" t="b">
-        <v>0</v>
-      </c>
-      <c r="P24" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q24" t="b">
-        <v>0</v>
-      </c>
+      <c r="O24" t="inlineStr"/>
+      <c r="P24" t="inlineStr"/>
+      <c r="Q24" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
